--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.2.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œfond of the world,â€� said Mrs.</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: personthher haggardface brightening prefer so much that you shouldnâ€™t see</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: 80</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -640,7 +644,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€œGo on; I comprehend you..To leave Southmeadow like this! He</t>
+          <t>L343: punctuation artifact: repeated periods :: “Go on; I comprehend you..To leave Southmeadow like this! He</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: ) 一 一</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dimly, â€œhe is very nice and warm- Very But you seem excited,</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -737,7 +741,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L325: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: * Â« Allow that Iâ€”erâ€”I will not speak magnificent, unparalleled recompense,</t>
+          <t>L344: line starts with digit/letter garbage token | suspicious token(s): 6Now (letter/digit mix) :: 6Now, Adelaide," he pursued, leaning | who had thought to leave it with ma-</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -791,19 +795,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: on him of $500, 000 â€”â€”"</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER :: - Despite his daring to live in so mother, youâ€™re wrong,â€� she insisted, Â« I</t>
+          <t>L198: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: scholar and a precious counsellor • as</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: I</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -824,7 +828,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L344: line starts with digit/letter garbage token | suspicious token(s): 6Now (letter/digit mix) :: 6Now, Adelaide," he pursued, leaning | who had thought to leave it with ma-</t>
+          <t>L382: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aWait (odd internal casing) :: aWait, please," she murmured, We can. talk just as well for a few min-</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -842,12 +846,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -874,19 +878,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ) ä¸€ ä¸€</t>
+          <t>L326: stray/suspicious non-ASCII glyph(s): U+8FCE CJK UNIFIED IDEOGRAPH-8FCE | isolated marker/symbol line :: … 迎</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gaeta nickeringinthe vansmile which feel. Promise youâ€™ll do as I ask, Car-</t>
+          <t>L385: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 79</t>
+          <t>L63: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>L769: punctuation artifact: repeated periods :: ...Â· $ 10, 000, 000</t>
+          <t>L769: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...· $ 10, 000, 000</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
@@ -907,7 +911,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L382: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aWait (odd internal casing) :: aWait, please," she murmured, We can. talk just as well for a few min-</t>
+          <t>L421: line starts with digit/letter garbage token | suspicious token(s): 0UVDOJUbUb (letter/digit mix) :: 0UVDOJUbUb</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -953,19 +957,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK :: ous ！ Had not Chalmers Channing told</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " If Iâ€™m not mistaken, Channing has Mrs. Courtaine turned and slipped back</t>
+          <t>L415: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: _'</t>
+          <t>L69: isolated marker/symbol line :: “I</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -986,7 +990,7 @@
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L421: line starts with digit/letter garbage token | suspicious token(s): 0UVDOJUbUb (letter/digit mix) :: 0UVDOJUbUb</t>
+          <t>L582: line starts with punctuation glued to text :: ** If you dumped a cart-load of gold at my feet</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1032,19 +1036,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œAllow that I-er-I will not speak</t>
+          <t>L547: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: ， and</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œYou hope such a thing!" fell in un- Ihad just declared herself. Still, her</t>
+          <t>L435: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | symbol-only separator/garbage line :: 2. €</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: '</t>
+          <t>L92: isolated marker/symbol line :: 79</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1061,7 +1065,7 @@
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L582: line starts with punctuation glued to text :: ** If you dumped a cart-load of gold at my feet</t>
+          <t>L712: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • My son, my boy," she said, catching</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1107,24 +1111,24 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN :: ible. But it had for him tÃ­us meaning:</t>
+          <t>L607: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: lip. " But the lad may rebel against any : Is undesired.â€�</t>
+          <t>L442: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: .</t>
+          <t>L98: isolated marker/symbol line :: _'</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1178,19 +1182,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: be â€”-</t>
+          <t>L820: stray/suspicious non-ASCII glyph(s): U+4ED3 CJK UNIFIED IDEOGRAPH-4ED3 | isolated marker/symbol line :: 仓</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - Then-pardon meâ€”you wish him to long where money is not only scrambled</t>
+          <t>L597: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: .</t>
+          <t>L99: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1217,12 +1221,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1239,21 +1243,17 @@
           <t>L300: suspicious token(s): 1down (letter/digit mix) :: times at smart dinner parties in New 1down for a dance of elves. On its light</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L326: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦ è¿Ž</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "M-yes. Andâ€”erâ€”marry here? strous, unthinkable.</t>
+          <t>L712: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • My son, my boy," she said, catching</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: a</t>
+          <t>L120: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1302,21 +1302,13 @@
           <t>L301: suspicious token(s): 1aris (letter/digit mix) | candidate OCR token mismatch vs other OCR: "Paris" vs "1aris" :: York, or perhaps in London or 1aris as green web, where not one of myriad tiny</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ous ï¼� Had not Chalmers Channing told</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of your own andâ€”of Archibaldâ€™s-grand- He bristled at those two curt mono-</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: 1</t>
+          <t>L121: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1343,12 +1335,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1365,21 +1357,13 @@
           <t>L344: line starts with digit/letter garbage token | suspicious token(s): 6Now (letter/digit mix) :: 6Now, Adelaide," he pursued, leaning | who had thought to leave it with ma-</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L510: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L170: isolated marker/symbol line :: 7</t>
+          <t>L143: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1428,26 +1412,18 @@
           <t>L382: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aWait (odd internal casing) :: aWait, please," she murmured, We can. talk just as well for a few min-</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L519: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: here to-day. It's this:â€œWhat wrong</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: musing. " Sheâ€™s merely transcendental</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L173: isolated marker/symbol line :: A</t>
+          <t>L150: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L391: isolated marker/symbol line :: 1-</t>
+          <t>L385: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1491,26 +1467,18 @@
           <t>L421: line starts with digit/letter garbage token | suspicious token(s): 0UVDOJUbUb (letter/digit mix) :: 0UVDOJUbUb</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "To repair?" she breathed.â€œHow?</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: scholar and a precious counsellor â€¢ as</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L170: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L393: isolated marker/symbol line :: 2=</t>
+          <t>L391: isolated marker/symbol line :: 1-</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1554,26 +1522,18 @@
           <t>L529: suspicious token(s): 62c (letter/digit mix) :: bought in Toronto at 62c ON THE</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: answered. â€œCuriosity has brought me.</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L217: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: My death, the professorâ€™s death (for no</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L212: isolated marker/symbol line :: e</t>
+          <t>L173: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: 173</t>
+          <t>L393: isolated marker/symbol line :: 2=</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1613,26 +1573,18 @@
           <t>L573: suspicious token(s): I11 (letter/digit mix) :: "Well, I tell you that first day is one I11</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L637: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œYou' were surprised by my answer?"?"</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L222: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: hereâ€”as one might say, among his own</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L227: isolated marker/symbol line :: 2</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: t</t>
+          <t>L395: isolated marker/symbol line :: 173</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1673,21 +1625,17 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L258: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A sad smile touched the ladyâ€™s lips. If a knife cutting into his flesh.</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L228: isolated marker/symbol line :: 3</t>
+          <t>L212: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L399: symbol-only separator/garbage line :: 401166:</t>
+          <t>L397: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1716,21 +1664,17 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: she had not already appealed to her ob-â€œIt is not only ridiculous," he per-</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L229: isolated marker/symbol line :: -</t>
+          <t>L227: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L401: isolated marker/symbol line :: A</t>
+          <t>L399: symbol-only separator/garbage line :: 401166:</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1759,21 +1703,17 @@
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L267: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: cultivated and honorable women. If he â€žYour son himself would never endorse</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L241: isolated marker/symbol line :: 6</t>
+          <t>L228: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: n</t>
+          <t>L401: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1802,21 +1742,17 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L278: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has lived contentedly until now, and â€œ Good day," he said, across one shoul-</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L285: isolated marker/symbol line :: '</t>
+          <t>L229: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L407: isolated marker/symbol line :: 0</t>
+          <t>L405: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1845,21 +1781,17 @@
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: now tossing them an inch or so upward, â€œ She is very probably not mad," ran</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L315: isolated marker/symbol line :: 97</t>
+          <t>L241: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L407: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1888,21 +1820,17 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œAs you please." . on the porch. He had no eye, no taste</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L319: isolated marker/symbol line :: .'</t>
+          <t>L285: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L419: isolated marker/symbol line :: 0</t>
+          <t>L415: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1931,21 +1859,17 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L320: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: reseat my having doneâ€”is an act now a distinct qualm of remorse for churlish-</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L323: isolated marker/symbol line :: ,'</t>
+          <t>L315: isolated marker/symbol line :: 97</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L423: isolated marker/symbol line :: 01</t>
+          <t>L419: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1974,21 +1898,17 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L325: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: * Â« Allow that Iâ€”erâ€”I will not speak magnificent, unparalleled recompense,</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L334: isolated marker/symbol line :: '</t>
+          <t>L319: isolated marker/symbol line :: .'</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L425: isolated marker/symbol line :: n</t>
+          <t>L423: isolated marker/symbol line :: 01</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2017,21 +1937,17 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€œGo on; I comprehend you..To leave Southmeadow like this! He</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L367: isolated marker/symbol line :: h</t>
+          <t>L323: isolated marker/symbol line :: ,'</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L427: isolated marker/symbol line :: 00</t>
+          <t>L425: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2056,21 +1972,17 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+02DC SMALL TILDE :: here to-day. Itâ€™s this : â€˜ What wrong cation, vexation, disgust.</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L406: isolated marker/symbol line :: 2</t>
+          <t>L326: stray/suspicious non-ASCII glyph(s): U+8FCE CJK UNIFIED IDEOGRAPH-8FCE | isolated marker/symbol line :: … 迎</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L427: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2095,21 +2007,17 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to repair." ,Iâ€žand the low of the pastured cow, and</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L407: isolated marker/symbol line :: 8</t>
+          <t>L334: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L597: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L435: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | symbol-only separator/garbage line :: 2. €</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2134,21 +2042,17 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œTo repair ?" she breathed. How? the slumbrous amethyst of the hills had</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L444: isolated marker/symbol line :: K</t>
+          <t>L367: isolated marker/symbol line :: h</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L633: isolated marker/symbol line :: /</t>
+          <t>L442: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2173,21 +2077,17 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ By aiding your son. , , neither answer for his</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L445: symbol-only separator/garbage line :: 60.</t>
+          <t>L406: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L656: isolated marker/symbol line :: 1</t>
+          <t>L597: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2212,21 +2112,17 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L356: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Aiding him? He needs no oneâ€™sing spirit nor blame for his</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L509: isolated marker/symbol line :: t</t>
+          <t>L407: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L668: isolated marker/symbol line :: 4</t>
+          <t>L633: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2251,21 +2147,17 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: She gave him none, but rose from her Youâ€™ve come back, then? she said,</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L510: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
+          <t>L444: isolated marker/symbol line :: K</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L805: isolated marker/symbol line :: 1</t>
+          <t>L656: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2290,21 +2182,17 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: chair instrsled face. Just then "Yes, Iâ€™ve come back, Adelaide," he</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L511: isolated marker/symbol line :: 2</t>
+          <t>L445: symbol-only separator/garbage line :: 60.</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 00</t>
+          <t>L668: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2329,21 +2217,17 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L378: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: hall-firm, buoyant, elastic. for a moment. Youâ€™re not very strong.</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L512: isolated marker/symbol line :: 0</t>
+          <t>L509: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L811: isolated marker/symbol line :: 00</t>
+          <t>L805: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2368,21 +2252,17 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mrs. Courtaine lifted one hand, and as youâ€™ve told me, and I hate to tax</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: +</t>
+          <t>L510: isolated marker/symbol line :: 》</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L813: isolated marker/symbol line :: 1</t>
+          <t>L809: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2407,21 +2287,17 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L385: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: ?"</t>
+          <t>L511: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L877: symbol-only separator/garbage line :: $10,000,000</t>
+          <t>L811: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2446,21 +2322,17 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L583: isolated marker/symbol line :: 66</t>
+          <t>L512: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L892: isolated marker/symbol line :: 1</t>
+          <t>L813: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2485,19 +2357,19 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L435: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: 2. â‚¬</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L682: isolated marker/symbol line :: 66</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L566: isolated marker/symbol line :: +</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L877: symbol-only separator/garbage line :: $10,000,000</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2520,19 +2392,19 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L702: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr"/>
+          <t>L578: isolated marker/symbol line :: ?"</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L892: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2555,16 +2427,12 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: than are the latter by constant feasts.â€”</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L805: isolated marker/symbol line :: 67</t>
+          <t>L583: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2590,16 +2458,12 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L597: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L808: isolated marker/symbol line :: .</t>
+          <t>L607: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2625,16 +2489,12 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L712: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ My son, my boy," she said, catching</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L820: isolated marker/symbol line :: ä»“</t>
+          <t>L682: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2660,14 +2520,14 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Why, mother ?"â€”</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>L702: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="O42" s="1" t="inlineStr"/>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
@@ -2691,14 +2551,14 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: disobeyedâ€”I mean you've never refused</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t>L769: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...· $ 10, 000, 000</t>
+        </is>
+      </c>
       <c r="O43" s="1" t="inlineStr"/>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
@@ -2722,14 +2582,14 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L731: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: You want me to avoid seeing ?"â€”</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t>L805: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
       <c r="O44" s="1" t="inlineStr"/>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
@@ -2753,14 +2613,14 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " Yes; thatâ€™s it; I want you to avoid</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>L808: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
       <c r="O45" s="1" t="inlineStr"/>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
@@ -2784,14 +2644,14 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Carrollâ€™s face flushed suddenly and his</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t>L820: stray/suspicious non-ASCII glyph(s): U+4ED3 CJK UNIFIED IDEOGRAPH-4ED3 | isolated marker/symbol line :: 仓</t>
+        </is>
+      </c>
       <c r="O46" s="1" t="inlineStr"/>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
@@ -2804,130 +2664,6 @@
       <c r="X46" s="1" t="inlineStr"/>
       <c r="Y46" s="1" t="inlineStr"/>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L743: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: that it is. There "â€”and she pushed him</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Dr. Pierceâ€™s Favorite Prescription is the best</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr"/>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L837: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜Prescription.â€™ I trust</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
-      <c r="R49" s="1" t="inlineStr"/>
-      <c r="S49" s="1" t="inlineStr"/>
-      <c r="T49" s="1" t="inlineStr"/>
-      <c r="U49" s="1" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
-      <c r="W49" s="1" t="inlineStr"/>
-      <c r="X49" s="1" t="inlineStr"/>
-      <c r="Y49" s="1" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr"/>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L856: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: DUNNâ€™S</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
-      <c r="R50" s="1" t="inlineStr"/>
-      <c r="S50" s="1" t="inlineStr"/>
-      <c r="T50" s="1" t="inlineStr"/>
-      <c r="U50" s="1" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
-      <c r="W50" s="1" t="inlineStr"/>
-      <c r="X50" s="1" t="inlineStr"/>
-      <c r="Y50" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
